--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD61CA2E-BF4A-4EA4-914C-67029B8245D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3669AB3C-5F47-4480-A225-33CA7B95C0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="321">
   <si>
     <t>Sl.No</t>
   </si>
@@ -604,9 +604,6 @@
     <t>ncg</t>
   </si>
   <si>
-    <t>guidewalls_side</t>
-  </si>
-  <si>
     <t>Side</t>
   </si>
   <si>
@@ -844,9 +841,6 @@
     <t>gwr/gwr_</t>
   </si>
   <si>
-    <t>avg_length_gwr</t>
-  </si>
-  <si>
     <t>gwr_-avg_length_gwr</t>
   </si>
   <si>
@@ -970,9 +964,6 @@
     <t>Canal_guidewall_height_increase_-chainage_canal_guidewall_height_increase_to</t>
   </si>
   <si>
-    <t>avg_length_gwl</t>
-  </si>
-  <si>
     <t>Left → E41</t>
   </si>
   <si>
@@ -1028,6 +1019,9 @@
   </si>
   <si>
     <t>gwbjl_-leakage_canal_length_gwbjl_leak2</t>
+  </si>
+  <si>
+    <t>ncg_-guidewalls_side</t>
   </si>
 </sst>
 </file>
@@ -2546,7 +2540,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>31</v>
@@ -2578,7 +2572,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>32</v>
@@ -2636,7 +2630,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D25" s="65" t="s">
         <v>145</v>
@@ -2698,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>34</v>
@@ -2758,7 +2752,7 @@
         <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D29" s="18" t="s">
         <v>151</v>
@@ -2790,7 +2784,7 @@
         <v>11</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D30" s="18" t="s">
         <v>154</v>
@@ -2822,7 +2816,7 @@
         <v>11</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D31" s="47" t="s">
         <v>155</v>
@@ -2854,7 +2848,7 @@
         <v>11</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D32" s="47" t="s">
         <v>159</v>
@@ -2886,7 +2880,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D33" s="47" t="s">
         <v>160</v>
@@ -2918,7 +2912,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>39</v>
@@ -2950,7 +2944,7 @@
         <v>11</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D35" s="52" t="s">
         <v>78</v>
@@ -2982,7 +2976,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D36" s="18" t="s">
         <v>41</v>
@@ -3014,7 +3008,7 @@
         <v>11</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D37" s="18" t="s">
         <v>42</v>
@@ -3046,7 +3040,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>43</v>
@@ -3078,7 +3072,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>44</v>
@@ -3110,7 +3104,7 @@
         <v>11</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D40" s="25" t="s">
         <v>167</v>
@@ -3119,7 +3113,7 @@
         <v>29</v>
       </c>
       <c r="F40" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>22</v>
@@ -3142,7 +3136,7 @@
         <v>11</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D41" s="25" t="s">
         <v>168</v>
@@ -3151,7 +3145,7 @@
         <v>29</v>
       </c>
       <c r="F41" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>22</v>
@@ -3174,7 +3168,7 @@
         <v>11</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>47</v>
@@ -3204,7 +3198,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>48</v>
@@ -3232,7 +3226,7 @@
         <v>11</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D44" s="18" t="s">
         <v>159</v>
@@ -3264,7 +3258,7 @@
         <v>11</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D45" s="18" t="s">
         <v>160</v>
@@ -3296,7 +3290,7 @@
         <v>11</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D46" s="18" t="s">
         <v>39</v>
@@ -3328,7 +3322,7 @@
         <v>11</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D47" s="18" t="s">
         <v>40</v>
@@ -3360,7 +3354,7 @@
         <v>11</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>41</v>
@@ -3392,7 +3386,7 @@
         <v>11</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D49" s="18" t="s">
         <v>42</v>
@@ -3424,7 +3418,7 @@
         <v>11</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D50" s="25" t="s">
         <v>45</v>
@@ -3433,7 +3427,7 @@
         <v>29</v>
       </c>
       <c r="F50" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>22</v>
@@ -3456,7 +3450,7 @@
         <v>11</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D51" s="25" t="s">
         <v>46</v>
@@ -3465,7 +3459,7 @@
         <v>29</v>
       </c>
       <c r="F51" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>22</v>
@@ -3488,7 +3482,7 @@
         <v>11</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>47</v>
@@ -3516,7 +3510,7 @@
         <v>11</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D53" s="22" t="s">
         <v>49</v>
@@ -3544,7 +3538,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D54" s="18" t="s">
         <v>36</v>
@@ -3576,7 +3570,7 @@
         <v>11</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D55" s="18" t="s">
         <v>37</v>
@@ -3608,7 +3602,7 @@
         <v>11</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>38</v>
@@ -3640,7 +3634,7 @@
         <v>11</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D57" s="18" t="s">
         <v>50</v>
@@ -3672,7 +3666,7 @@
         <v>11</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>51</v>
@@ -3704,7 +3698,7 @@
         <v>11</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>39</v>
@@ -3736,10 +3730,10 @@
         <v>11</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E60" s="21" t="s">
         <v>29</v>
@@ -3768,7 +3762,7 @@
         <v>11</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>52</v>
@@ -3777,7 +3771,7 @@
         <v>29</v>
       </c>
       <c r="F61" s="69" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>22</v>
@@ -3800,7 +3794,7 @@
         <v>11</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D62" s="18" t="s">
         <v>53</v>
@@ -3809,7 +3803,7 @@
         <v>29</v>
       </c>
       <c r="F62" s="69" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>22</v>
@@ -3832,16 +3826,16 @@
         <v>11</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F63" s="40" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>22</v>
@@ -3864,16 +3858,16 @@
         <v>11</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E64" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F64" s="71" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G64" s="16" t="s">
         <v>22</v>
@@ -3896,7 +3890,7 @@
         <v>11</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D65" s="25" t="s">
         <v>45</v>
@@ -3905,7 +3899,7 @@
         <v>29</v>
       </c>
       <c r="F65" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>22</v>
@@ -3928,7 +3922,7 @@
         <v>11</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D66" s="25" t="s">
         <v>46</v>
@@ -3937,7 +3931,7 @@
         <v>29</v>
       </c>
       <c r="F66" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>22</v>
@@ -3960,7 +3954,7 @@
         <v>11</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D67" s="23" t="s">
         <v>47</v>
@@ -3988,7 +3982,7 @@
         <v>11</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D68" s="22" t="s">
         <v>54</v>
@@ -4016,7 +4010,7 @@
         <v>11</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D69" s="18" t="s">
         <v>55</v>
@@ -4048,7 +4042,7 @@
         <v>11</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D70" s="18" t="s">
         <v>56</v>
@@ -4080,16 +4074,16 @@
         <v>11</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D71" s="47" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E71" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F71" s="71" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>22</v>
@@ -4112,16 +4106,16 @@
         <v>11</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D72" s="47" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E72" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F72" s="71" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>22</v>
@@ -4144,16 +4138,16 @@
         <v>11</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E73" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F73" s="71" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>22</v>
@@ -4176,7 +4170,7 @@
         <v>11</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D74" s="18" t="s">
         <v>57</v>
@@ -4185,7 +4179,7 @@
         <v>29</v>
       </c>
       <c r="F74" s="71" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>22</v>
@@ -4208,7 +4202,7 @@
         <v>11</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D75" s="28" t="s">
         <v>58</v>
@@ -4236,7 +4230,7 @@
         <v>11</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D76" s="18" t="s">
         <v>59</v>
@@ -4268,7 +4262,7 @@
         <v>11</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D77" s="23" t="s">
         <v>60</v>
@@ -4296,7 +4290,7 @@
         <v>11</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D78" s="22" t="s">
         <v>61</v>
@@ -4324,7 +4318,7 @@
         <v>11</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D79" s="30" t="s">
         <v>62</v>
@@ -4356,7 +4350,7 @@
         <v>11</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D80" s="18" t="s">
         <v>63</v>
@@ -4388,7 +4382,7 @@
         <v>11</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D81" s="18" t="s">
         <v>64</v>
@@ -4420,7 +4414,7 @@
         <v>11</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D82" s="18" t="s">
         <v>65</v>
@@ -4452,7 +4446,7 @@
         <v>11</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D83" s="18" t="s">
         <v>66</v>
@@ -4484,7 +4478,7 @@
         <v>11</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D84" s="31" t="s">
         <v>67</v>
@@ -4516,7 +4510,7 @@
         <v>11</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D85" s="18" t="s">
         <v>68</v>
@@ -4548,7 +4542,7 @@
         <v>11</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D86" s="18" t="s">
         <v>69</v>
@@ -4580,7 +4574,7 @@
         <v>11</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D87" s="18" t="s">
         <v>70</v>
@@ -4612,7 +4606,7 @@
         <v>11</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D88" s="31" t="s">
         <v>71</v>
@@ -4644,7 +4638,7 @@
         <v>11</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D89" s="18" t="s">
         <v>64</v>
@@ -4676,7 +4670,7 @@
         <v>11</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D90" s="83" t="s">
         <v>72</v>
@@ -4708,7 +4702,7 @@
         <v>11</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D91" s="18" t="s">
         <v>73</v>
@@ -4740,7 +4734,7 @@
         <v>11</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D92" s="31" t="s">
         <v>74</v>
@@ -4772,7 +4766,7 @@
         <v>11</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D93" s="18" t="s">
         <v>75</v>
@@ -4804,7 +4798,7 @@
         <v>11</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D94" s="18" t="s">
         <v>76</v>
@@ -4860,7 +4854,7 @@
         <v>170</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>5</v>
@@ -4890,10 +4884,10 @@
         <v>173</v>
       </c>
       <c r="L1" s="70" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="30">
@@ -4901,40 +4895,40 @@
         <v>180</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C2" s="71" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D2" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="L2" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="E2" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="L2" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -4942,40 +4936,40 @@
         <v>180</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C3" s="71" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I3" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L3" s="71" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="8" customFormat="1">
@@ -4983,25 +4977,25 @@
         <v>180</v>
       </c>
       <c r="B4" s="77" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C4" s="73" t="s">
+        <v>320</v>
+      </c>
+      <c r="D4" s="74" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="74" t="s">
-        <v>182</v>
-      </c>
       <c r="E4" s="74" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F4" s="74" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G4" s="74" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H4" s="74" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I4" s="72" t="s">
         <v>22</v>
@@ -5009,10 +5003,10 @@
       <c r="J4" s="72"/>
       <c r="K4" s="72"/>
       <c r="L4" s="74" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M4" s="78" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="8" customFormat="1">
@@ -5020,22 +5014,22 @@
         <v>180</v>
       </c>
       <c r="B5" s="77" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E5" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F5" s="72" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H5" s="74" t="s">
         <v>174</v>
@@ -5046,10 +5040,10 @@
       <c r="J5" s="72"/>
       <c r="K5" s="72"/>
       <c r="L5" s="74" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M5" s="78" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="8" customFormat="1">
@@ -5057,22 +5051,22 @@
         <v>180</v>
       </c>
       <c r="B6" s="77" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C6" s="73" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D6" s="74" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E6" s="74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F6" s="72" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G6" s="74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H6" s="74" t="s">
         <v>174</v>
@@ -5083,74 +5077,74 @@
       <c r="J6" s="72"/>
       <c r="K6" s="72"/>
       <c r="L6" s="74" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M6" s="78" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="8" customFormat="1" ht="30">
       <c r="A7" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="32" t="s">
-        <v>189</v>
-      </c>
       <c r="C7" s="73" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D7" s="74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L7" s="71" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="30">
       <c r="A8" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>189</v>
-      </c>
       <c r="C8" s="71" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="G8" s="32" t="s">
         <v>184</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="F8" s="72" t="s">
-        <v>266</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>185</v>
       </c>
       <c r="H8" s="32" t="s">
         <v>174</v>
@@ -5159,35 +5153,35 @@
         <v>22</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="30">
       <c r="A9" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B9" s="32" t="s">
-        <v>189</v>
-      </c>
       <c r="C9" s="71" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D9" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="F9" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" s="32" t="s">
         <v>184</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="F9" s="72" t="s">
-        <v>266</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>185</v>
       </c>
       <c r="H9" s="32" t="s">
         <v>174</v>
@@ -5196,404 +5190,404 @@
         <v>22</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="30">
       <c r="A10" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>189</v>
-      </c>
       <c r="C10" s="71" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D10" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E10" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="F10" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="G10" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="H10" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="K10" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="L10" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="M10" s="26" t="s">
         <v>273</v>
-      </c>
-      <c r="E10" s="72" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="72" t="s">
-        <v>183</v>
-      </c>
-      <c r="G10" s="72" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="72" t="s">
-        <v>183</v>
-      </c>
-      <c r="I10" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="72" t="s">
-        <v>183</v>
-      </c>
-      <c r="K10" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="L10" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="M10" s="26" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="30">
       <c r="A11" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>189</v>
-      </c>
       <c r="C11" s="71" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E11" s="72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F11" s="72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G11" s="72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H11" s="72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J11" s="72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K11" s="32" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L11" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="30">
+      <c r="A12" s="71" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="C12" s="71" t="s">
         <v>268</v>
       </c>
-      <c r="M11" s="26" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="71" t="s">
+      <c r="D12" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="K12" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="L12" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="30">
+      <c r="A13" s="71" t="s">
+        <v>258</v>
+      </c>
+      <c r="B13" s="71" t="s">
         <v>259</v>
       </c>
-      <c r="B12" s="71" t="s">
-        <v>260</v>
-      </c>
-      <c r="C12" s="71" t="s">
-        <v>261</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="F12" s="32" t="s">
+      <c r="C13" s="71" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="K13" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="L13" s="71" t="s">
         <v>266</v>
       </c>
-      <c r="G12" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="32" t="s">
-        <v>305</v>
-      </c>
-      <c r="K12" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="L12" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="M12" s="79" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="71" t="s">
-        <v>259</v>
-      </c>
-      <c r="B13" s="71" t="s">
-        <v>260</v>
-      </c>
-      <c r="C13" s="71" t="s">
-        <v>303</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="G13" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="K13" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="L13" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="M13" s="79" t="s">
-        <v>269</v>
+      <c r="M13" s="9" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="30">
       <c r="A14" s="71" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="71" t="s">
         <v>259</v>
       </c>
-      <c r="B14" s="71" t="s">
+      <c r="C14" s="71" t="s">
+        <v>274</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="K14" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="L14" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="71" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="C14" s="71" t="s">
-        <v>270</v>
-      </c>
-      <c r="D14" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="E14" s="32" t="s">
+      <c r="D15" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="E15" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="L15" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="M15" s="79" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="71" t="s">
+        <v>258</v>
+      </c>
+      <c r="B16" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="71" t="s">
+        <v>261</v>
+      </c>
+      <c r="D16" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="G14" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="I14" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="K14" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="L14" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="M14" s="9" t="s">
+      <c r="E16" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="L16" s="32" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="30">
-      <c r="A15" s="71" t="s">
-        <v>259</v>
-      </c>
-      <c r="B15" s="71" t="s">
-        <v>260</v>
-      </c>
-      <c r="C15" s="71" t="s">
-        <v>272</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="G15" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="I15" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="K15" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="L15" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="30">
-      <c r="A16" s="71" t="s">
-        <v>259</v>
-      </c>
-      <c r="B16" s="71" t="s">
-        <v>260</v>
-      </c>
-      <c r="C16" s="71" t="s">
-        <v>276</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="K16" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="L16" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>278</v>
+      <c r="M16" s="79" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="30">
       <c r="A17" s="71" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C17" s="71" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D17" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="K17" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="L17" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="G17" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="I17" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="K17" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="L17" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="30">
       <c r="A18" s="71" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C18" s="71" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G18" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I18" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J18" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K18" s="32" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L18" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="30">
       <c r="A19" s="71" t="s">
+        <v>282</v>
+      </c>
+      <c r="B19" s="71" t="s">
         <v>284</v>
       </c>
-      <c r="B19" s="71" t="s">
-        <v>286</v>
-      </c>
       <c r="C19" s="71" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F19" s="32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G19" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H19" s="70" t="s">
         <v>174</v>
@@ -5602,37 +5596,37 @@
         <v>22</v>
       </c>
       <c r="J19" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K19" s="32"/>
       <c r="L19" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="30">
       <c r="A20" s="71" t="s">
+        <v>282</v>
+      </c>
+      <c r="B20" s="71" t="s">
         <v>284</v>
       </c>
-      <c r="B20" s="71" t="s">
-        <v>286</v>
-      </c>
       <c r="C20" s="71" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F20" s="32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G20" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H20" s="70" t="s">
         <v>174</v>
@@ -5641,160 +5635,160 @@
         <v>22</v>
       </c>
       <c r="J20" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K20" s="32"/>
       <c r="L20" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="30">
       <c r="A21" s="71" t="s">
+        <v>283</v>
+      </c>
+      <c r="B21" s="71" t="s">
         <v>285</v>
       </c>
-      <c r="B21" s="71" t="s">
-        <v>287</v>
-      </c>
       <c r="C21" s="71" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G21" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I21" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J21" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K21" s="32" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L21" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="30">
       <c r="A22" s="71" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C22" s="71" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D22" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="K22" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="L22" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="M22" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="K22" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="L22" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="30">
       <c r="A23" s="71" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B23" s="71" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C23" s="71" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G23" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H23" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I23" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J23" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K23" s="32" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L23" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="45">
       <c r="A24" s="71" t="s">
+        <v>283</v>
+      </c>
+      <c r="B24" s="71" t="s">
         <v>285</v>
       </c>
-      <c r="B24" s="71" t="s">
-        <v>287</v>
-      </c>
       <c r="C24" s="71" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E24" s="70" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F24" s="32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G24" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H24" s="70" t="s">
         <v>174</v>
@@ -5803,37 +5797,37 @@
         <v>22</v>
       </c>
       <c r="J24" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="45">
       <c r="A25" s="71" t="s">
+        <v>283</v>
+      </c>
+      <c r="B25" s="71" t="s">
         <v>285</v>
       </c>
-      <c r="B25" s="71" t="s">
-        <v>287</v>
-      </c>
       <c r="C25" s="71" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E25" s="70" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G25" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H25" s="70" t="s">
         <v>174</v>
@@ -5842,37 +5836,37 @@
         <v>22</v>
       </c>
       <c r="J25" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="67" customFormat="1" ht="30">
       <c r="A26" s="32" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C26" s="71" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E26" s="70" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F26" s="70" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G26" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H26" s="70" t="s">
         <v>174</v>
@@ -5881,98 +5875,98 @@
         <v>22</v>
       </c>
       <c r="J26" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K26" s="32" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L26" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="30">
       <c r="A27" s="76" t="s">
+        <v>286</v>
+      </c>
+      <c r="B27" s="76" t="s">
         <v>288</v>
       </c>
-      <c r="B27" s="76" t="s">
-        <v>290</v>
-      </c>
       <c r="C27" s="71" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D27" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="K27" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="L27" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="M27" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="F27" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="G27" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="H27" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="I27" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="K27" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="L27" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="30">
       <c r="A28" s="76" t="s">
+        <v>286</v>
+      </c>
+      <c r="B28" s="76" t="s">
         <v>288</v>
       </c>
-      <c r="B28" s="76" t="s">
+      <c r="C28" s="71" t="s">
         <v>290</v>
       </c>
-      <c r="C28" s="71" t="s">
-        <v>292</v>
-      </c>
       <c r="D28" s="32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G28" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H28" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I28" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J28" s="32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K28" s="32" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L28" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
